--- a/data/trans_dic/P38A-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P38A-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a</t>
+          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,6; 93,57</t>
+          <t>87,48; 93,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,87; 90,56</t>
+          <t>83,74; 90,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84,61; 91,31</t>
+          <t>84,64; 91,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88,03; 94,71</t>
+          <t>88,04; 94,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,89; 95,86</t>
+          <t>90,49; 95,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,54; 92,89</t>
+          <t>87,8; 92,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,07; 93,33</t>
+          <t>89,11; 93,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87,76; 92,13</t>
+          <t>87,73; 92,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>86,94; 91,33</t>
+          <t>86,95; 91,24</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>87,14; 93,05</t>
+          <t>86,89; 92,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84,49; 91,26</t>
+          <t>84,31; 91,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,75; 91,95</t>
+          <t>85,78; 92,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90,94; 96,44</t>
+          <t>90,63; 96,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,65; 93,07</t>
+          <t>86,93; 93,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,27; 92,19</t>
+          <t>86,01; 92,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,22; 94,06</t>
+          <t>89,91; 93,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>86,41; 91,25</t>
+          <t>86,71; 91,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86,81; 91,53</t>
+          <t>86,92; 91,41</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,26; 92,12</t>
+          <t>87,22; 92,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>85,14; 90,94</t>
+          <t>84,76; 90,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,38; 90,62</t>
+          <t>22,89; 90,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87,31; 94,42</t>
+          <t>87,08; 94,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>87,41; 95,79</t>
+          <t>87,55; 95,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,7; 96,04</t>
+          <t>89,77; 96,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>88,04; 92,07</t>
+          <t>87,94; 92,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>86,48; 91,31</t>
+          <t>86,84; 91,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,41; 91,58</t>
+          <t>30,59; 91,57</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>86,02; 90,0</t>
+          <t>85,69; 89,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,83; 88,95</t>
+          <t>84,71; 88,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82,14; 87,99</t>
+          <t>82,39; 88,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86,33; 90,9</t>
+          <t>86,47; 91,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,53; 91,0</t>
+          <t>87,09; 91,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,28; 96,58</t>
+          <t>90,27; 96,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,73; 89,83</t>
+          <t>86,78; 89,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>86,34; 89,44</t>
+          <t>86,41; 89,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,85; 92,17</t>
+          <t>86,85; 92,54</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>79,19; 86,21</t>
+          <t>79,37; 86,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,79; 85,21</t>
+          <t>79,19; 85,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,51; 87,69</t>
+          <t>80,41; 87,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90,66; 94,39</t>
+          <t>90,5; 94,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>87,46; 91,85</t>
+          <t>87,8; 92,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,7; 92,23</t>
+          <t>61,91; 92,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,06; 90,66</t>
+          <t>87,06; 90,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>84,53; 88,3</t>
+          <t>84,39; 88,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>69,78; 89,32</t>
+          <t>69,88; 89,28</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44,21; 56,24</t>
+          <t>44,68; 56,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,65; 59,34</t>
+          <t>47,07; 59,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,02; 55,8</t>
+          <t>34,59; 55,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83,64; 88,13</t>
+          <t>84,13; 88,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>86,43; 90,37</t>
+          <t>86,61; 90,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,0; 86,97</t>
+          <t>81,08; 87,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76,98; 81,4</t>
+          <t>76,83; 81,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>78,96; 83,3</t>
+          <t>79,02; 83,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70,81; 78,47</t>
+          <t>70,56; 78,3</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>84,0; 86,56</t>
+          <t>84,15; 86,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82,31; 84,86</t>
+          <t>82,29; 84,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59,52; 84,34</t>
+          <t>62,99; 84,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>88,82; 90,77</t>
+          <t>88,78; 90,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,84; 90,84</t>
+          <t>88,73; 90,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,23; 90,8</t>
+          <t>82,17; 90,75</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,8; 88,45</t>
+          <t>86,62; 88,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>86,02; 87,6</t>
+          <t>85,96; 87,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>70,12; 86,92</t>
+          <t>72,18; 86,97</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a</t>
+          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>380401; 406307</t>
+          <t>379842; 404747</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>359011; 387654</t>
+          <t>358443; 387587</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>427457; 461303</t>
+          <t>427632; 460560</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>275896; 296828</t>
+          <t>275916; 296893</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>314507; 331686</t>
+          <t>313133; 331243</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>391722; 415657</t>
+          <t>392892; 415965</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>665933; 697772</t>
+          <t>666245; 698522</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>679351; 713122</t>
+          <t>679061; 712976</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>828301; 870119</t>
+          <t>828347; 869266</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>364165; 388859</t>
+          <t>363101; 388522</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>317837; 343300</t>
+          <t>317176; 342584</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>387794; 415832</t>
+          <t>387926; 416224</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>306571; 325116</t>
+          <t>305538; 324311</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>322583; 346468</t>
+          <t>323610; 346234</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>330051; 352701</t>
+          <t>329052; 352819</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>681194; 710141</t>
+          <t>678821; 707428</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>646732; 682942</t>
+          <t>648962; 682926</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>724684; 764071</t>
+          <t>725576; 763047</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>548361; 578897</t>
+          <t>548101; 578175</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>441894; 472006</t>
+          <t>439967; 470367</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>136182; 605583</t>
+          <t>152974; 606738</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>227130; 245601</t>
+          <t>226513; 244994</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>144446; 158293</t>
+          <t>144680; 158274</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>149715; 160308</t>
+          <t>149844; 160396</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>782218; 818075</t>
+          <t>781390; 819281</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>591788; 624831</t>
+          <t>594242; 625562</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>228916; 764845</t>
+          <t>255508; 764785</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>988223; 1033966</t>
+          <t>984478; 1033461</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>968768; 1015799</t>
+          <t>967364; 1013984</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>850018; 910573</t>
+          <t>852582; 914997</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>661846; 696895</t>
+          <t>662913; 697924</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>712212; 748995</t>
+          <t>716847; 750233</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>883022; 944658</t>
+          <t>882931; 941161</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1661268; 1720602</t>
+          <t>1662178; 1720364</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1696753; 1757648</t>
+          <t>1698080; 1755800</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1748232; 1855298</t>
+          <t>1748309; 1862811</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>400813; 436349</t>
+          <t>401723; 435355</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>485423; 524980</t>
+          <t>487893; 524929</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>382445; 416585</t>
+          <t>381963; 416415</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>688599; 716948</t>
+          <t>687409; 718439</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>643779; 676064</t>
+          <t>646241; 678264</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>519145; 775958</t>
+          <t>520864; 774905</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1101912; 1147577</t>
+          <t>1101939; 1146736</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1142939; 1193882</t>
+          <t>1141016; 1192732</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>918532; 1175816</t>
+          <t>919862; 1175248</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>116692; 148449</t>
+          <t>117934; 148862</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>131161; 166845</t>
+          <t>132340; 166128</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>81823; 134200</t>
+          <t>83181; 133980</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>919792; 969160</t>
+          <t>925116; 970384</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>932526; 975131</t>
+          <t>934475; 973326</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>616701; 662129</t>
+          <t>617300; 664742</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1049692; 1109909</t>
+          <t>1047605; 1110539</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1073959; 1133076</t>
+          <t>1074829; 1132136</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>709450; 786133</t>
+          <t>706937; 784496</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2855645; 2942410</t>
+          <t>2860712; 2942397</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2767802; 2853368</t>
+          <t>2767022; 2854007</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2009597; 2847479</t>
+          <t>2126538; 2842811</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3141066; 3210028</t>
+          <t>3139806; 3211167</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3128726; 3198998</t>
+          <t>3124922; 3196021</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2906252; 3248565</t>
+          <t>2939970; 3246706</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6020164; 6134636</t>
+          <t>6008308; 6124052</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5921742; 6030694</t>
+          <t>5917685; 6029508</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4876191; 6043921</t>
+          <t>5019076; 6047663</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P38A-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P38A-Clase-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,36%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>87,48; 93,21</t>
+          <t>87,51; 93,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83,74; 90,55</t>
+          <t>83,74; 90,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84,64; 91,16</t>
+          <t>84,43; 90,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88,04; 94,73</t>
+          <t>88,13; 94,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,49; 95,73</t>
+          <t>90,57; 95,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,8; 92,96</t>
+          <t>87,91; 93,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,11; 93,43</t>
+          <t>88,78; 93,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87,73; 92,11</t>
+          <t>87,89; 92,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>86,95; 91,24</t>
+          <t>87,17; 91,17</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,19%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,89; 92,97</t>
+          <t>87,48; 93,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>84,31; 91,07</t>
+          <t>84,13; 91,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85,78; 92,04</t>
+          <t>85,57; 91,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90,63; 96,2</t>
+          <t>90,62; 96,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,93; 93,01</t>
+          <t>86,43; 93,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,01; 92,22</t>
+          <t>86,38; 92,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,91; 93,7</t>
+          <t>89,59; 93,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>86,71; 91,24</t>
+          <t>86,63; 91,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>86,92; 91,41</t>
+          <t>86,83; 91,25</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>90,02%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,22; 92,01</t>
+          <t>87,32; 92,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,76; 90,62</t>
+          <t>85,35; 90,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,89; 90,79</t>
+          <t>85,25; 91,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87,08; 94,18</t>
+          <t>87,22; 94,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>87,55; 95,78</t>
+          <t>87,88; 95,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>89,77; 96,1</t>
+          <t>89,33; 95,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,94; 92,21</t>
+          <t>88,11; 92,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>86,84; 91,42</t>
+          <t>86,58; 91,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,59; 91,57</t>
+          <t>87,43; 92,3</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>87,71%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85,69; 89,96</t>
+          <t>85,98; 89,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,71; 88,79</t>
+          <t>84,85; 88,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82,39; 88,42</t>
+          <t>82,72; 87,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86,47; 91,03</t>
+          <t>86,21; 90,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,09; 91,15</t>
+          <t>86,66; 90,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,27; 96,22</t>
+          <t>88,97; 92,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,78; 89,81</t>
+          <t>86,76; 89,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>86,41; 89,35</t>
+          <t>86,35; 89,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,85; 92,54</t>
+          <t>85,76; 89,34</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>79,37; 86,01</t>
+          <t>79,5; 86,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,19; 85,21</t>
+          <t>79,02; 85,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80,41; 87,66</t>
+          <t>74,83; 82,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90,5; 94,59</t>
+          <t>90,9; 94,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>87,8; 92,15</t>
+          <t>87,47; 91,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,91; 92,1</t>
+          <t>87,91; 91,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,06; 90,6</t>
+          <t>86,79; 90,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>84,39; 88,21</t>
+          <t>84,55; 88,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>69,88; 89,28</t>
+          <t>83,34; 87,35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>73,48%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44,68; 56,4</t>
+          <t>44,67; 56,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>47,07; 59,08</t>
+          <t>46,79; 59,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,59; 55,71</t>
+          <t>32,9; 51,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84,13; 88,24</t>
+          <t>83,85; 87,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>86,61; 90,21</t>
+          <t>86,36; 90,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,08; 87,31</t>
+          <t>79,18; 85,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76,83; 81,44</t>
+          <t>76,84; 81,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>79,02; 83,24</t>
+          <t>79,27; 83,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70,56; 78,3</t>
+          <t>69,57; 76,83</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>85,77%</t>
         </is>
       </c>
     </row>
@@ -1338,37 +1338,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>84,15; 86,56</t>
+          <t>84,05; 86,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>82,29; 84,88</t>
+          <t>82,38; 84,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62,99; 84,2</t>
+          <t>80,9; 84,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>88,78; 90,8</t>
+          <t>88,69; 90,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,73; 90,75</t>
+          <t>88,8; 90,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,17; 90,75</t>
+          <t>87,47; 89,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,62; 88,29</t>
+          <t>86,68; 88,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>72,18; 86,97</t>
+          <t>84,85; 86,81</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>446169</t>
+          <t>485590</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>405565</t>
+          <t>442853</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>851734</t>
+          <t>928443</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>379842; 404747</t>
+          <t>380011; 406325</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>358443; 387587</t>
+          <t>358462; 387089</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>427632; 460560</t>
+          <t>464860; 500659</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>275916; 296893</t>
+          <t>276191; 296672</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>313133; 331243</t>
+          <t>313396; 331291</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>392892; 415965</t>
+          <t>429375; 454247</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>666245; 698522</t>
+          <t>663740; 697483</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>679061; 712976</t>
+          <t>680321; 712746</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>828347; 869266</t>
+          <t>905678; 947317</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>403499</t>
+          <t>430099</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>342270</t>
+          <t>378236</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>745769</t>
+          <t>808335</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>363101; 388522</t>
+          <t>365570; 389601</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>317176; 342584</t>
+          <t>316492; 342978</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>387926; 416224</t>
+          <t>413461; 443004</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>305538; 324311</t>
+          <t>305494; 324321</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>323610; 346234</t>
+          <t>321759; 346813</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>329052; 352819</t>
+          <t>365505; 390478</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>678821; 707428</t>
+          <t>676392; 708181</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>648962; 682926</t>
+          <t>648359; 682074</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>725576; 763047</t>
+          <t>786959; 827094</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>380385</t>
+          <t>418655</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>156009</t>
+          <t>174689</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>536394</t>
+          <t>593345</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>548101; 578175</t>
+          <t>548708; 579099</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>439967; 470367</t>
+          <t>442996; 471275</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>152974; 606738</t>
+          <t>402060; 433528</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>226513; 244994</t>
+          <t>226873; 245292</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>144680; 158274</t>
+          <t>145226; 158314</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>149844; 160396</t>
+          <t>167492; 179770</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>781390; 819281</t>
+          <t>782903; 819164</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>594242; 625562</t>
+          <t>592452; 625692</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>255508; 764785</t>
+          <t>576260; 608336</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>884558</t>
+          <t>965452</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>908671</t>
+          <t>782562</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1793229</t>
+          <t>1748013</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>984478; 1033461</t>
+          <t>987719; 1033124</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>967364; 1013984</t>
+          <t>969013; 1014918</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>852582; 914997</t>
+          <t>936285; 994759</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>662913; 697924</t>
+          <t>660941; 696841</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>716847; 750233</t>
+          <t>713320; 748940</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>882931; 941161</t>
+          <t>766182; 798267</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1662178; 1720364</t>
+          <t>1661844; 1719649</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1698080; 1755800</t>
+          <t>1696854; 1753997</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1748309; 1862811</t>
+          <t>1709202; 1780521</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>400452</t>
+          <t>449848</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>706132</t>
+          <t>748326</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1106584</t>
+          <t>1198174</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>401723; 435355</t>
+          <t>402429; 438158</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>487893; 524929</t>
+          <t>486841; 526221</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>381963; 416415</t>
+          <t>424987; 470216</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>687409; 718439</t>
+          <t>690453; 718232</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>646241; 678264</t>
+          <t>643858; 676661</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>520864; 774905</t>
+          <t>730385; 761844</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1101939; 1146736</t>
+          <t>1098589; 1144305</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1141016; 1192732</t>
+          <t>1143280; 1195728</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>919862; 1175248</t>
+          <t>1165752; 1221878</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>106082</t>
+          <t>99652</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>641761</t>
+          <t>695004</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>747843</t>
+          <t>794655</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>117934; 148862</t>
+          <t>117901; 150042</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>132340; 166128</t>
+          <t>131549; 167325</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>83181; 133980</t>
+          <t>78050; 123193</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>925116; 970384</t>
+          <t>922063; 965951</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>934475; 973326</t>
+          <t>931804; 974903</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>617300; 664742</t>
+          <t>668467; 720766</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1047605; 1110539</t>
+          <t>1047744; 1107957</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1074829; 1132136</t>
+          <t>1078225; 1134639</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>706937; 784496</t>
+          <t>752392; 830920</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2621144</t>
+          <t>2849295</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3160409</t>
+          <t>3221669</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5781553</t>
+          <t>6070964</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2860712; 2942397</t>
+          <t>2857130; 2943387</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2767022; 2854007</t>
+          <t>2770006; 2854323</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2126538; 2842811</t>
+          <t>2784973; 2897360</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3139806; 3211167</t>
+          <t>3136602; 3210221</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3124922; 3196021</t>
+          <t>3127348; 3196419</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2939970; 3246706</t>
+          <t>3179860; 3261695</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6008308; 6124052</t>
+          <t>6012219; 6129029</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5917685; 6029508</t>
+          <t>5918047; 6029542</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5019076; 6047663</t>
+          <t>6005577; 6144343</t>
         </is>
       </c>
     </row>
